--- a/Indomie Clients Details/Gourmet/Gourmet_24-06-26.xlsx
+++ b/Indomie Clients Details/Gourmet/Gourmet_24-06-26.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A701F328-2B80-4701-8950-32735A200E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{065EBDFE-ADBD-465B-BB72-6114C7B3BED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -3910,7 +3910,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -3938,7 +3938,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -5151,7 +5151,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -5179,7 +5179,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -6392,7 +6392,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -6420,7 +6420,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -7632,7 +7632,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -7660,7 +7660,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -8874,7 +8874,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -8902,7 +8902,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -10109,7 +10109,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -10137,7 +10137,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -11389,7 +11389,7 @@
       <c r="M4" s="375"/>
       <c r="N4" s="391">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="391"/>
       <c r="P4" s="391"/>
@@ -11423,7 +11423,7 @@
       <c r="M5" s="375"/>
       <c r="N5" s="391">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="376"/>
       <c r="P5" s="376"/>
@@ -12745,7 +12745,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -12773,7 +12773,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -13980,7 +13980,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -14008,7 +14008,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -15220,7 +15220,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -15248,7 +15248,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -19211,7 +19211,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -19239,7 +19239,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -20451,7 +20451,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -20479,7 +20479,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -21686,7 +21686,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -21714,7 +21714,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -22926,7 +22926,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -22954,7 +22954,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -24153,7 +24153,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -24174,7 +24174,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -25335,7 +25335,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -25356,7 +25356,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -26275,7 +26275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" ht="21.5" x14ac:dyDescent="0.35">
       <c r="B32" s="326"/>
       <c r="C32" s="327"/>
       <c r="D32" s="327"/>
@@ -26517,7 +26517,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -26538,7 +26538,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -27463,7 +27463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" ht="21.5" x14ac:dyDescent="0.35">
       <c r="B32" s="326"/>
       <c r="C32" s="327"/>
       <c r="D32" s="327"/>
@@ -27703,7 +27703,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -27724,7 +27724,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -28643,7 +28643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" ht="21.5" x14ac:dyDescent="0.35">
       <c r="B32" s="326"/>
       <c r="C32" s="327"/>
       <c r="D32" s="327"/>
@@ -28885,7 +28885,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -28906,7 +28906,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -29825,7 +29825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" ht="21.5" x14ac:dyDescent="0.35">
       <c r="B32" s="326"/>
       <c r="C32" s="327"/>
       <c r="D32" s="327"/>
@@ -30065,7 +30065,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -30085,7 +30085,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -30996,7 +30996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" ht="21.5" x14ac:dyDescent="0.35">
       <c r="B32" s="326"/>
       <c r="C32" s="327"/>
       <c r="D32" s="327"/>
@@ -31249,7 +31249,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -31277,7 +31277,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -33032,7 +33032,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -33052,7 +33052,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -33963,7 +33963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" ht="21.5" x14ac:dyDescent="0.35">
       <c r="B32" s="326"/>
       <c r="C32" s="327"/>
       <c r="D32" s="327"/>
@@ -34269,7 +34269,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -34297,7 +34297,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -35512,7 +35512,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -35540,7 +35540,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -36754,7 +36754,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -36782,7 +36782,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -37992,7 +37992,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -38020,7 +38020,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -39230,7 +39230,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -39258,7 +39258,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
@@ -40472,7 +40472,7 @@
       <c r="M4" s="296"/>
       <c r="N4" s="297">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="297"/>
       <c r="P4" s="297"/>
@@ -40500,7 +40500,7 @@
       <c r="M5" s="296"/>
       <c r="N5" s="297">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="295"/>
       <c r="P5" s="295"/>
